--- a/w5-zone3-consumption-gating/Zone3_Gating_Test_Tracker.xlsx
+++ b/w5-zone3-consumption-gating/Zone3_Gating_Test_Tracker.xlsx
@@ -562,7 +562,6 @@
           <t>Zone 3 Consumption Gating — POC Test Tracker</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr"/>
@@ -588,7 +587,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>claude/solution_design.md — single source of truth. Option IDs (O1..O22) and the verified-facts table (section 11) are referenced from this workbook.</t>
+          <t>solution_design.md — single source of truth. Option IDs (O1..O22) and the verified-facts table (section 11) are referenced from this workbook.</t>
         </is>
       </c>
     </row>

--- a/w5-zone3-consumption-gating/Zone3_Gating_Test_Tracker.xlsx
+++ b/w5-zone3-consumption-gating/Zone3_Gating_Test_Tracker.xlsx
@@ -2483,7 +2483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3307,106 +3307,114 @@
       <c r="N18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>TC-016</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Stored data is plaintext — unbind the policy and read it back</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>SC-06</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>O10</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>01_governance_survival.sql</t>
+        </is>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>Inference, not documented</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="inlineStr">
+        <is>
+          <t>Real value reads back in the clear once the policy is unbound, proving storage was never masked</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I19" s="18" t="inlineStr"/>
+      <c r="J19" s="19" t="inlineStr"/>
+      <c r="K19" s="19" t="inlineStr"/>
+      <c r="L19" s="19" t="inlineStr"/>
+      <c r="M19" s="19" t="inlineStr"/>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>Underpins all of Part B. If storage were masked on write, losing a tag would be harmless and R15 would not exist. Replaces the claim previously resting on an earlier POC capture</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>TC-020</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>O11 — group publish inside one transaction, no mixed state</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>SC-02, SC-03, SC-13</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>O11</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>02_atomicity_publication.sql</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>ASSUMPTION: the reader NEVER observes distinct_cycles = 2. All old before COMMIT, all new after</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr"/>
-      <c r="J19" s="9" t="inlineStr"/>
-      <c r="K19" s="9" t="inlineStr"/>
-      <c r="L19" s="9" t="inlineStr"/>
-      <c r="M19" s="9" t="inlineStr"/>
-      <c r="N19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>TC-021</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>Table-level SWAP — do grants follow the object?</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>SC-16</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>O9</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>02_atomicity_publication.sql</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>Not documented</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>ASSUMPTION: grants follow the OBJECT, not the name. The ALTER TABLE page is silent on this</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="14" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr"/>
-      <c r="K20" s="7" t="inlineStr"/>
-      <c r="L20" s="7" t="inlineStr"/>
-      <c r="M20" s="7" t="inlineStr"/>
-      <c r="N20" s="8" t="inlineStr"/>
+      <c r="I20" s="21" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr"/>
+      <c r="K20" s="9" t="inlineStr"/>
+      <c r="L20" s="9" t="inlineStr"/>
+      <c r="M20" s="9" t="inlineStr"/>
+      <c r="N20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>TC-022</t>
+          <t>TC-021</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Schema SWAP — grants, schema USAGE, and previous-version reachability</t>
+          <t>Table-level SWAP — do grants follow the object?</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -3416,7 +3424,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>O16</t>
+          <t>O9</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -3426,12 +3434,12 @@
       </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>Partly verified</t>
+          <t>Not documented</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>Documented: privileges on the schemas and their objects swap. UNDOCUMENTED: can the reporting role still query STG.* after the swap?</t>
+          <t>ASSUMPTION: grants follow the OBJECT, not the name. The ALTER TABLE page is silent on this</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr"/>
@@ -3445,17 +3453,17 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>TC-023</t>
+          <t>TC-022</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Schema SWAP — held-open read spanning the swap</t>
+          <t>Schema SWAP — grants, schema USAGE, and previous-version reachability</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>SC-02, SC-13</t>
+          <t>SC-16</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -3470,12 +3478,12 @@
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>POC evidence</t>
+          <t>Partly verified</t>
         </is>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>A query beginning before the swap returns one whole consistent cycle. Extends POC02's held-open join to 4 objects</t>
+          <t>Documented: privileges on the schemas and their objects swap. UNDOCUMENTED: can the reporting role still query STG.* after the swap?</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
@@ -3489,22 +3497,22 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>TC-024</t>
+          <t>TC-023</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>O11 ROLLBACK — a failed cycle publishes nothing</t>
+          <t>Schema SWAP — held-open read spanning the swap</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>SC-10</t>
+          <t>SC-02, SC-13</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>O11</t>
+          <t>O16</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -3514,12 +3522,12 @@
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>POC evidence</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>After ROLLBACK the published group is unchanged by the abandoned cycle</t>
+          <t>A query beginning before the swap returns one whole consistent cycle. Extends POC02's held-open join to 4 objects</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr"/>
@@ -3533,22 +3541,22 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>TC-025</t>
+          <t>TC-024</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Single-table INSERT OVERWRITE — never empty, never partial</t>
+          <t>O11 ROLLBACK — a failed cycle publishes nothing</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>SC-01, SC-13</t>
+          <t>SC-10</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>O10</t>
+          <t>O11</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
@@ -3563,7 +3571,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>The reader's rowcount is always the old count or the new count. Never 0, never a partial count</t>
+          <t>After ROLLBACK the published group is unchanged by the abandoned cycle</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
@@ -3577,22 +3585,22 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>TC-026</t>
+          <t>TC-025</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>COUNTER-EXAMPLE: TRUNCATE + INSERT is not atomic</t>
+          <t>Single-table INSERT OVERWRITE — never empty, never partial</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>SC-01</t>
+          <t>SC-01, SC-13</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>O10</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -3607,7 +3615,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>The reader DOES observe 0 rows. Evidence that a TRUNCATE-then-load pattern cannot satisfy Part A</t>
+          <t>The reader's rowcount is always the old count or the new count. Never 0, never a partial count</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr"/>
@@ -3621,37 +3629,37 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>TC-027</t>
+          <t>TC-026</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>V-a — a view over gated tables inherits consistency, zero view changes</t>
+          <t>COUNTER-EXAMPLE: TRUNCATE + INSERT is not atomic</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>SC-04</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>O11</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>03_views_shape_dependencies.sql</t>
+          <t>02_atomicity_publication.sql</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>Design logic</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>mixed_rows = 0 before and after publication; the view's DDL is byte-identical throughout</t>
+          <t>The reader DOES observe 0 rows. Evidence that a TRUNCATE-then-load pattern cannot satisfy Part A</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr"/>
@@ -3665,12 +3673,12 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>TC-028</t>
+          <t>TC-027</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>View SQL unchanged across a schema swap (name resolution)</t>
+          <t>V-a — a view over gated tables inherits consistency, zero view changes</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -3680,7 +3688,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>O16</t>
+          <t>O11</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -3690,12 +3698,12 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Design logic</t>
         </is>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>The view returns the new cycle without being edited. Proves C1 holds for O16</t>
+          <t>mixed_rows = 0 before and after publication; the view's DDL is byte-identical throughout</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr"/>
@@ -3709,12 +3717,12 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>TC-029</t>
+          <t>TC-028</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>A view INSIDE a swapped schema, self-referencing by full path</t>
+          <t>View SQL unchanged across a schema swap (name resolution)</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -3734,12 +3742,12 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>POC evidence</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>After the swap at least one of the two names resolves to the wrong storage. Why views live outside the swapped pair</t>
+          <t>The view returns the new cycle without being edited. Proves C1 holds for O16</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr"/>
@@ -3751,215 +3759,215 @@
       <c r="N28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>TC-029</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>A view INSIDE a swapped schema, self-referencing by full path</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>SC-04</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>O16</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>03_views_shape_dependencies.sql</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>POC evidence</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>After the swap at least one of the two names resolves to the wrong storage. Why views live outside the swapped pair</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="14" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>TC-030</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Clustering key survival — INSERT OVERWRITE vs CTAS</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>SC-17</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>O8, O10</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>03_views_shape_dependencies.sql</t>
         </is>
       </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>INSERT OVERWRITE target keeps CLUSTER BY; the CTAS target has no cluster_by</t>
         </is>
       </c>
-      <c r="H29" s="9" t="inlineStr"/>
-      <c r="I29" s="21" t="inlineStr"/>
-      <c r="J29" s="9" t="inlineStr"/>
-      <c r="K29" s="9" t="inlineStr"/>
-      <c r="L29" s="9" t="inlineStr"/>
-      <c r="M29" s="9" t="inlineStr"/>
-      <c r="N29" s="10" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr"/>
+      <c r="I30" s="21" t="inlineStr"/>
+      <c r="J30" s="9" t="inlineStr"/>
+      <c r="K30" s="9" t="inlineStr"/>
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="9" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>TC-031</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>Streams on a published object after each mechanism</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>SC-18</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>O8, O10, O16</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>03_views_shape_dependencies.sql</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>ASSUMPTION: INSERT OVERWRITE advances the stream normally; OR REPLACE leaves it stale. Capture the exact error</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="14" t="inlineStr"/>
-      <c r="J30" s="7" t="inlineStr"/>
-      <c r="K30" s="7" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr"/>
-      <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="8" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="14" t="inlineStr"/>
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>TC-032</t>
         </is>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>DDL inside an O11 transaction silently commits</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>SC-02</t>
         </is>
       </c>
-      <c r="D31" s="10" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>O11</t>
         </is>
       </c>
-      <c r="E31" s="10" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>02_atomicity_publication.sql</t>
         </is>
       </c>
-      <c r="F31" s="10" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>The DDL commits the preceding statement, so ROLLBACK leaves a MIXED state published. Justifies a hard build rule</t>
         </is>
       </c>
-      <c r="H31" s="9" t="inlineStr"/>
-      <c r="I31" s="21" t="inlineStr"/>
-      <c r="J31" s="9" t="inlineStr"/>
-      <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="9" t="inlineStr"/>
-      <c r="M31" s="9" t="inlineStr"/>
-      <c r="N31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>TC-033</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>INSERT OVERWRITE on a Snowflake-managed Iceberg table</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>SC-21</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>O14</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>03_views_shape_dependencies.sql</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>Not documented</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>ASSUMPTION: supported, since v3 documents INSERT and TRUNCATE. Needs an external volume, else record as Blocked</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="14" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
-      <c r="K32" s="7" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr"/>
-      <c r="M32" s="7" t="inlineStr"/>
-      <c r="N32" s="8" t="inlineStr"/>
+      <c r="H32" s="9" t="inlineStr"/>
+      <c r="I32" s="21" t="inlineStr"/>
+      <c r="J32" s="9" t="inlineStr"/>
+      <c r="K32" s="9" t="inlineStr"/>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="9" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>TC-034</t>
+          <t>TC-033</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Gate FAIL — publish nothing, consumers keep the previous version</t>
+          <t>INSERT OVERWRITE on a Snowflake-managed Iceberg table</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>SC-10</t>
+          <t>SC-21</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>gate</t>
+          <t>O14</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>04_gate_rollback_control.sql</t>
+          <t>03_views_shape_dependencies.sql</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>Design logic</t>
+          <t>Not documented</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>At least one gate check FAILs; the publish is not attempted; the published cycle is unchanged</t>
+          <t>ASSUMPTION: supported, since v3 documents INSERT and TRUNCATE. Needs an external volume, else record as Blocked</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr"/>
@@ -3973,17 +3981,17 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>TC-035</t>
+          <t>TC-034</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Business-authorised partial release, on the record</t>
+          <t>Gate FAIL — publish nothing, consumers keep the previous version</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>SC-11</t>
+          <t>SC-10</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -4003,7 +4011,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>Authorisation record names who, when, why and which jobs failed. Publication logged as AUTHORISED_PARTIAL</t>
+          <t>At least one gate check FAILs; the publish is not attempted; the published cycle is unchanged</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr"/>
@@ -4017,22 +4025,22 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>TC-036</t>
+          <t>TC-035</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Rollback via re-swap</t>
+          <t>Business-authorised partial release, on the record</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>SC-12</t>
+          <t>SC-11</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>O16</t>
+          <t>gate</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
@@ -4042,12 +4050,12 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Design logic</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>One further ALTER SCHEMA SWAP WITH returns consumers to the previous version</t>
+          <t>Authorisation record names who, when, why and which jobs failed. Publication logged as AUTHORISED_PARTIAL</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr"/>
@@ -4061,12 +4069,12 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>TC-037</t>
+          <t>TC-036</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Rollback via re-publish from the retained previous version</t>
+          <t>Rollback via re-swap</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -4076,7 +4084,7 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>O11</t>
+          <t>O16</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
@@ -4091,7 +4099,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>One more transaction restores the prior version. The window closes when the next cycle overwrites staging</t>
+          <t>One further ALTER SCHEMA SWAP WITH returns consumers to the previous version</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr"/>
@@ -4103,208 +4111,204 @@
       <c r="N36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>TC-037</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Rollback via re-publish from the retained previous version</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>SC-12</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>O11</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>04_gate_rollback_control.sql</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>One more transaction restores the prior version. The window closes when the next cycle overwrites staging</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="14" t="inlineStr"/>
+      <c r="J37" s="7" t="inlineStr"/>
+      <c r="K37" s="7" t="inlineStr"/>
+      <c r="L37" s="7" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="8" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>TC-038</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>Publication record written and queryable (alerting basis)</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C38" s="16" t="inlineStr">
         <is>
           <t>SC-07</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>gate</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>04_gate_rollback_control.sql</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>Design logic</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>One row per group per cycle, and a staleness query Ops can alert on</t>
         </is>
       </c>
-      <c r="H37" s="17" t="inlineStr"/>
-      <c r="I37" s="18" t="inlineStr"/>
-      <c r="J37" s="19" t="inlineStr"/>
-      <c r="K37" s="19" t="inlineStr"/>
-      <c r="L37" s="19" t="inlineStr"/>
-      <c r="M37" s="19" t="inlineStr"/>
-      <c r="N37" s="16" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="H38" s="17" t="inlineStr"/>
+      <c r="I38" s="18" t="inlineStr"/>
+      <c r="J38" s="19" t="inlineStr"/>
+      <c r="K38" s="19" t="inlineStr"/>
+      <c r="L38" s="19" t="inlineStr"/>
+      <c r="M38" s="19" t="inlineStr"/>
+      <c r="N38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>TC-039</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>NON-REINSTATEMENT — a governance-removed tag must not come back</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>SC-08</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>O10, O16</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>04_gate_rollback_control.sql</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>ASSUMPTION: O10 leaves it removed; O16 REINSTATES it unless the gate reconciled staging first</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="I38" s="14" t="inlineStr"/>
-      <c r="J38" s="7" t="inlineStr"/>
-      <c r="K38" s="7" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr"/>
-      <c r="M38" s="7" t="inlineStr"/>
-      <c r="N38" s="8" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="I39" s="14" t="inlineStr"/>
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr"/>
+      <c r="L39" s="7" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="8" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>TC-040</t>
         </is>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>Sizing — which objects the reporting identities actually read</t>
         </is>
       </c>
-      <c r="C39" s="16" t="inlineStr">
+      <c r="C40" s="16" t="inlineStr">
         <is>
           <t>SC-19</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="E39" s="16" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>05_sizing_performance.sql</t>
         </is>
       </c>
-      <c r="F39" s="16" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>Design logic</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>A list materially shorter than the full view estate. That gap is the saving from gating only what is consumed</t>
         </is>
       </c>
-      <c r="H39" s="17" t="inlineStr"/>
-      <c r="I39" s="18" t="inlineStr"/>
-      <c r="J39" s="19" t="inlineStr"/>
-      <c r="K39" s="19" t="inlineStr"/>
-      <c r="L39" s="19" t="inlineStr"/>
-      <c r="M39" s="19" t="inlineStr"/>
-      <c r="N39" s="16" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>TC-041</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Group membership, and do groups fit inside ONE schema?</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>SC-19</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>O11, O16</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>05_sizing_performance.sql</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
-        <is>
-          <t>Design logic</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>tables_to_gate per schema = the effort number. Any schemas_spanned &gt; 1 means O16 is not viable for that group</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>CRITICAL</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr"/>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr"/>
-      <c r="M40" s="7" t="inlineStr"/>
-      <c r="N40" s="8" t="inlineStr"/>
+      <c r="H40" s="17" t="inlineStr"/>
+      <c r="I40" s="18" t="inlineStr"/>
+      <c r="J40" s="19" t="inlineStr"/>
+      <c r="K40" s="19" t="inlineStr"/>
+      <c r="L40" s="19" t="inlineStr"/>
+      <c r="M40" s="19" t="inlineStr"/>
+      <c r="N40" s="16" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>TC-050</t>
+          <t>TC-041</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Performance — INSERT OVERWRITE vs CTAS, narrow (4 cols)</t>
+          <t>Group membership, and do groups fit inside ONE schema?</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>SC-20</t>
+          <t>SC-19</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>O8, O10</t>
+          <t>O11, O16</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
@@ -4314,15 +4318,19 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>No benchmark</t>
+          <t>Design logic</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>Expect broadly comparable, SELECT-dominated. Record median seconds, GB written, and whether clustering survived</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr"/>
+          <t>tables_to_gate per schema = the effort number. Any schemas_spanned &gt; 1 means O16 is not viable for that group</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
       <c r="I41" s="14" t="inlineStr"/>
       <c r="J41" s="7" t="inlineStr"/>
       <c r="K41" s="7" t="inlineStr"/>
@@ -4333,12 +4341,12 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>TC-051</t>
+          <t>TC-050</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Performance — INSERT OVERWRITE vs CTAS, wide (60 cols)</t>
+          <t>Performance — INSERT OVERWRITE vs CTAS, narrow (4 cols)</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -4363,7 +4371,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>As TC-050 at 60 columns, to see whether width changes the relationship</t>
+          <t>Expect broadly comparable, SELECT-dominated. Record median seconds, GB written, and whether clustering survived</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr"/>
@@ -4377,12 +4385,12 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>TC-052</t>
+          <t>TC-051</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Performance — O11 publish-transaction duration by group size</t>
+          <t>Performance — INSERT OVERWRITE vs CTAS, wide (60 cols)</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -4392,7 +4400,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>O11</t>
+          <t>O8, O10</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
@@ -4407,7 +4415,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>The cost of the second write. Must stay well inside the documented 4-hour non-blocking transaction limit</t>
+          <t>As TC-050 at 60 columns, to see whether width changes the relationship</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr"/>
@@ -4419,14 +4427,14 @@
       <c r="N43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>TC-053</t>
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>TC-052</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Performance — O16 schema-swap duration by object count</t>
+          <t>Performance — O11 publish-transaction duration by group size</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -4436,7 +4444,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>O16</t>
+          <t>O11</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -4451,16 +4459,60 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>Expect effectively constant and sub-second regardless of volume. TC-052 vs TC-053 is the trade-off made concrete</t>
+          <t>The cost of the second write. Must stay well inside the documented 4-hour non-blocking transaction limit</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr"/>
+      <c r="I44" s="14" t="inlineStr"/>
       <c r="J44" s="7" t="inlineStr"/>
       <c r="K44" s="7" t="inlineStr"/>
       <c r="L44" s="7" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
       <c r="N44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>TC-053</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Performance — O16 schema-swap duration by object count</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>SC-20</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>O16</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>05_sizing_performance.sql</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>No benchmark</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>Expect effectively constant and sub-second regardless of volume. TC-052 vs TC-053 is the trade-off made concrete</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr"/>
+      <c r="I45" s="7" t="inlineStr"/>
+      <c r="J45" s="7" t="inlineStr"/>
+      <c r="K45" s="7" t="inlineStr"/>
+      <c r="L45" s="7" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+      <c r="N45" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5269,7 +5321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5602,29 +5654,24 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>TC-020</t>
+          <t>TC-016</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>O11 — group publish inside one transaction, no mixed state</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="7" t="inlineStr"/>
-      <c r="F19" s="14" t="inlineStr"/>
-      <c r="G19" s="8" t="inlineStr"/>
+          <t>Stored data is plaintext — unbind the policy and read it back</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>TC-021</t>
+          <t>TC-020</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Table-level SWAP — do grants follow the object?</t>
+          <t>O11 — group publish inside one transaction, no mixed state</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr"/>
@@ -5636,12 +5683,12 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>TC-022</t>
+          <t>TC-021</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>Schema SWAP — grants, schema USAGE, and previous-version reachability</t>
+          <t>Table-level SWAP — do grants follow the object?</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr"/>
@@ -5653,12 +5700,12 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>TC-023</t>
+          <t>TC-022</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Schema SWAP — held-open read spanning the swap</t>
+          <t>Schema SWAP — grants, schema USAGE, and previous-version reachability</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr"/>
@@ -5670,12 +5717,12 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>TC-024</t>
+          <t>TC-023</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>O11 ROLLBACK — a failed cycle publishes nothing</t>
+          <t>Schema SWAP — held-open read spanning the swap</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr"/>
@@ -5687,12 +5734,12 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>TC-025</t>
+          <t>TC-024</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Single-table INSERT OVERWRITE — never empty, never partial</t>
+          <t>O11 ROLLBACK — a failed cycle publishes nothing</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr"/>
@@ -5704,12 +5751,12 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>TC-026</t>
+          <t>TC-025</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>COUNTER-EXAMPLE: TRUNCATE + INSERT is not atomic</t>
+          <t>Single-table INSERT OVERWRITE — never empty, never partial</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr"/>
@@ -5721,12 +5768,12 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>TC-027</t>
+          <t>TC-026</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>V-a — a view over gated tables inherits consistency, zero view changes</t>
+          <t>COUNTER-EXAMPLE: TRUNCATE + INSERT is not atomic</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr"/>
@@ -5738,12 +5785,12 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>TC-028</t>
+          <t>TC-027</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>View SQL unchanged across a schema swap (name resolution)</t>
+          <t>V-a — a view over gated tables inherits consistency, zero view changes</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr"/>
@@ -5755,12 +5802,12 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>TC-029</t>
+          <t>TC-028</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>A view INSIDE a swapped schema, self-referencing by full path</t>
+          <t>View SQL unchanged across a schema swap (name resolution)</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr"/>
@@ -5772,12 +5819,12 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>TC-030</t>
+          <t>TC-029</t>
         </is>
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Clustering key survival — INSERT OVERWRITE vs CTAS</t>
+          <t>A view INSIDE a swapped schema, self-referencing by full path</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr"/>
@@ -5789,12 +5836,12 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>TC-031</t>
+          <t>TC-030</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Streams on a published object after each mechanism</t>
+          <t>Clustering key survival — INSERT OVERWRITE vs CTAS</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr"/>
@@ -5806,12 +5853,12 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>TC-032</t>
+          <t>TC-031</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>DDL inside an O11 transaction silently commits</t>
+          <t>Streams on a published object after each mechanism</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr"/>
@@ -5823,12 +5870,12 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>TC-033</t>
+          <t>TC-032</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>INSERT OVERWRITE on a Snowflake-managed Iceberg table</t>
+          <t>DDL inside an O11 transaction silently commits</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr"/>
@@ -5840,12 +5887,12 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>TC-034</t>
+          <t>TC-033</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Gate FAIL — publish nothing, consumers keep the previous version</t>
+          <t>INSERT OVERWRITE on a Snowflake-managed Iceberg table</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr"/>
@@ -5857,12 +5904,12 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>TC-035</t>
+          <t>TC-034</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Business-authorised partial release, on the record</t>
+          <t>Gate FAIL — publish nothing, consumers keep the previous version</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr"/>
@@ -5874,12 +5921,12 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>TC-036</t>
+          <t>TC-035</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Rollback via re-swap</t>
+          <t>Business-authorised partial release, on the record</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr"/>
@@ -5891,12 +5938,12 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>TC-037</t>
+          <t>TC-036</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Rollback via re-publish from the retained previous version</t>
+          <t>Rollback via re-swap</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr"/>
@@ -5908,12 +5955,12 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>TC-038</t>
+          <t>TC-037</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Publication record written and queryable (alerting basis)</t>
+          <t>Rollback via re-publish from the retained previous version</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr"/>
@@ -5925,12 +5972,12 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>TC-039</t>
+          <t>TC-038</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>NON-REINSTATEMENT — a governance-removed tag must not come back</t>
+          <t>Publication record written and queryable (alerting basis)</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr"/>
@@ -5942,12 +5989,12 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>TC-040</t>
+          <t>TC-039</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Sizing — which objects the reporting identities actually read</t>
+          <t>NON-REINSTATEMENT — a governance-removed tag must not come back</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr"/>
@@ -5959,12 +6006,12 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>TC-041</t>
+          <t>TC-040</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Group membership, and do groups fit inside ONE schema?</t>
+          <t>Sizing — which objects the reporting identities actually read</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr"/>
@@ -5976,12 +6023,12 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>TC-050</t>
+          <t>TC-041</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Performance — INSERT OVERWRITE vs CTAS, narrow (4 cols)</t>
+          <t>Group membership, and do groups fit inside ONE schema?</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr"/>
@@ -5993,12 +6040,12 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>TC-051</t>
+          <t>TC-050</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Performance — INSERT OVERWRITE vs CTAS, wide (60 cols)</t>
+          <t>Performance — INSERT OVERWRITE vs CTAS, narrow (4 cols)</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr"/>
@@ -6010,12 +6057,12 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>TC-052</t>
+          <t>TC-051</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Performance — O11 publish-transaction duration by group size</t>
+          <t>Performance — INSERT OVERWRITE vs CTAS, wide (60 cols)</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr"/>
@@ -6027,12 +6074,12 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>TC-053</t>
+          <t>TC-052</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Performance — O16 schema-swap duration by object count</t>
+          <t>Performance — O11 publish-transaction duration by group size</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr"/>
@@ -6040,6 +6087,23 @@
       <c r="E44" s="7" t="inlineStr"/>
       <c r="F44" s="14" t="inlineStr"/>
       <c r="G44" s="8" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>TC-053</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Performance — O16 schema-swap duration by object count</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr"/>
+      <c r="D45" s="7" t="inlineStr"/>
+      <c r="E45" s="7" t="inlineStr"/>
+      <c r="F45" s="14" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/w5-zone3-consumption-gating/Zone3_Gating_Test_Tracker.xlsx
+++ b/w5-zone3-consumption-gating/Zone3_Gating_Test_Tracker.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test_Cases" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenario_Option" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence_Log" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirement_Coverage" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +52,10 @@
       <b val="1"/>
       <color rgb="00DA291C"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="7">
@@ -112,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -183,6 +188,14 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2483,12 +2496,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -2515,60 +2528,65 @@
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
+          <t>Requirement(s)</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Option(s)</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Script</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Documented status</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>Expected result</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Evidence file</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Tester</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Date run</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Snowflake version</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Notes / what a failure invalidates</t>
         </is>
@@ -2577,18 +2595,18 @@
     <row r="2">
       <c r="A2" s="13" t="n"/>
       <c r="B2" s="8" t="n"/>
-      <c r="C2" s="8" t="n"/>
       <c r="D2" s="8" t="n"/>
       <c r="E2" s="8" t="n"/>
       <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="14" t="n"/>
-      <c r="J2" s="7" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="7" t="n"/>
+      <c r="J2" s="14" t="n"/>
       <c r="K2" s="7" t="n"/>
       <c r="L2" s="7" t="n"/>
       <c r="M2" s="7" t="n"/>
-      <c r="N2" s="8" t="n"/>
+      <c r="N2" s="7" t="n"/>
+      <c r="O2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
@@ -2603,36 +2621,41 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>O10</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Design logic</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>email tagged PII_EMAIL; MASK_EMAIL bound; reader has SELECT; owner = POC_ROLE</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr"/>
-      <c r="I3" s="14" t="inlineStr"/>
-      <c r="J3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr"/>
+      <c r="J3" s="14" t="inlineStr"/>
       <c r="K3" s="7" t="inlineStr"/>
       <c r="L3" s="7" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
+      <c r="N3" s="7" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -2647,36 +2670,41 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
           <t>SC-06, SC-14</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>O8</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Tag GONE, policy GONE, reader SELECT GONE, owner = executing role. Reproduces POC02's 4 -&gt; 0</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr"/>
-      <c r="I4" s="14" t="inlineStr"/>
-      <c r="J4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="14" t="inlineStr"/>
       <c r="K4" s="7" t="inlineStr"/>
       <c r="L4" s="7" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
+      <c r="N4" s="7" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -2691,36 +2719,41 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
+          <t>R14, R18</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
           <t>SC-06, SC-14</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>O8</t>
         </is>
       </c>
-      <c r="E5" s="16" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F5" s="16" t="inlineStr">
+      <c r="G5" s="16" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G5" s="16" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>Tag PRESENT, reader SELECT PRESENT, but OWNER = executing role (COPY GRANTS excludes OWNERSHIP)</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr"/>
-      <c r="I5" s="18" t="inlineStr"/>
-      <c r="J5" s="19" t="inlineStr"/>
+      <c r="I5" s="17" t="inlineStr"/>
+      <c r="J5" s="18" t="inlineStr"/>
       <c r="K5" s="19" t="inlineStr"/>
       <c r="L5" s="19" t="inlineStr"/>
       <c r="M5" s="19" t="inlineStr"/>
-      <c r="N5" s="16" t="inlineStr"/>
+      <c r="N5" s="19" t="inlineStr"/>
+      <c r="O5" s="16" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -2735,40 +2768,45 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>O10</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>ASSUMPTION: tag PRESENT on EMAIL, identical to TC-001, because the object is not replaced</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="I6" s="18" t="inlineStr"/>
-      <c r="J6" s="19" t="inlineStr"/>
+      <c r="J6" s="18" t="inlineStr"/>
       <c r="K6" s="19" t="inlineStr"/>
       <c r="L6" s="19" t="inlineStr"/>
       <c r="M6" s="19" t="inlineStr"/>
-      <c r="N6" s="16" t="inlineStr"/>
+      <c r="N6" s="19" t="inlineStr"/>
+      <c r="O6" s="16" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
@@ -2783,40 +2821,45 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
+          <t>R14, R28</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
           <t>SC-06, SC-15</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>O10</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>ASSUMPTION: POC_ROLE sees clear text; reporting role sees a 64-char SHA2 hash</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="I7" s="21" t="inlineStr"/>
-      <c r="J7" s="9" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
       <c r="K7" s="9" t="inlineStr"/>
       <c r="L7" s="9" t="inlineStr"/>
       <c r="M7" s="9" t="inlineStr"/>
-      <c r="N7" s="10" t="inlineStr"/>
+      <c r="N7" s="9" t="inlineStr"/>
+      <c r="O7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -2831,36 +2874,41 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
           <t>SC-05</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>O10</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>03_views_shape_dependencies.sql</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>Data lands from the existing view; tag, policy, grants and owner on the pre-deployed table all unchanged</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr"/>
-      <c r="I8" s="18" t="inlineStr"/>
-      <c r="J8" s="19" t="inlineStr"/>
+      <c r="I8" s="17" t="inlineStr"/>
+      <c r="J8" s="18" t="inlineStr"/>
       <c r="K8" s="19" t="inlineStr"/>
       <c r="L8" s="19" t="inlineStr"/>
       <c r="M8" s="19" t="inlineStr"/>
-      <c r="N8" s="16" t="inlineStr"/>
+      <c r="N8" s="19" t="inlineStr"/>
+      <c r="O8" s="16" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -2875,40 +2923,45 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
           <t>SC-14</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>O10</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="H9" s="8" t="inlineStr">
         <is>
           <t>ASSUMPTION: owner UNCHANGED. This is the whole reason O10 is preferred over O8</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
+      <c r="J9" s="14" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr"/>
       <c r="L9" s="7" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="8" t="inlineStr"/>
+      <c r="N9" s="7" t="inlineStr"/>
+      <c r="O9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
@@ -2923,36 +2976,41 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>O10</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Reader SELECT present, identical to TC-001. Docs: 'does not affect the access control privileges on the table'</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="14" t="inlineStr"/>
-      <c r="J10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="14" t="inlineStr"/>
       <c r="K10" s="7" t="inlineStr"/>
       <c r="L10" s="7" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="7" t="inlineStr"/>
+      <c r="O10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
@@ -2967,36 +3025,41 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>O9</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>Tag PRESENT, policy PRESENT, reader SELECT PRESENT</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="14" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr"/>
       <c r="L11" s="7" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
-      <c r="N11" s="8" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
+      <c r="O11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
@@ -3011,36 +3074,41 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>O9</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="H12" s="8" t="inlineStr">
         <is>
           <t>Tag PRESENT. Column-level tags travel across schemas, so clone is not restricted to one schema</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="14" t="inlineStr"/>
-      <c r="J12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="14" t="inlineStr"/>
       <c r="K12" s="7" t="inlineStr"/>
       <c r="L12" s="7" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
-      <c r="N12" s="8" t="inlineStr"/>
+      <c r="N12" s="7" t="inlineStr"/>
+      <c r="O12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
@@ -3055,36 +3123,41 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
+          <t>R14, R16</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>O9</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>The clone is NOT masked by the source schema's tag-based policy. Justifies column-level binding</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr"/>
-      <c r="J13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr"/>
+      <c r="J13" s="14" t="inlineStr"/>
       <c r="K13" s="7" t="inlineStr"/>
       <c r="L13" s="7" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="8" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
@@ -3099,36 +3172,41 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
           <t>SC-09</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>O18</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Existing EMAIL tag intact; new column added; grants, owner and row count unchanged. New column carries NO tag</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="14" t="inlineStr"/>
-      <c r="J14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr"/>
+      <c r="J14" s="14" t="inlineStr"/>
       <c r="K14" s="7" t="inlineStr"/>
       <c r="L14" s="7" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
-      <c r="N14" s="8" t="inlineStr"/>
+      <c r="N14" s="7" t="inlineStr"/>
+      <c r="O14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="20" t="inlineStr">
@@ -3143,36 +3221,41 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
           <t>SC-09</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>O8</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Tag LOST on the renamed column. An ordinary view edit becomes a silent protection gap</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="21" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="21" t="inlineStr"/>
       <c r="K15" s="9" t="inlineStr"/>
       <c r="L15" s="9" t="inlineStr"/>
       <c r="M15" s="9" t="inlineStr"/>
-      <c r="N15" s="10" t="inlineStr"/>
+      <c r="N15" s="9" t="inlineStr"/>
+      <c r="O15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
@@ -3187,36 +3270,41 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
           <t>SC-09</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
         <is>
           <t>O15</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="F16" s="8" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="H16" s="8" t="inlineStr">
         <is>
           <t>ASSUMPTION: no-op — no error and NO data change. Record whether it errors, warns or succeeds silently</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="14" t="inlineStr"/>
-      <c r="J16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr"/>
+      <c r="J16" s="14" t="inlineStr"/>
       <c r="K16" s="7" t="inlineStr"/>
       <c r="L16" s="7" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
-      <c r="N16" s="8" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
@@ -3231,36 +3319,41 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
+          <t>R15, R27</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
           <t>SC-15</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>O8, O10, O11</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>POC evidence</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="H17" s="8" t="inlineStr">
         <is>
           <t>An allowed role writes CLEAR values. A role the policy does not allow writes SHA2 hashes stored as though genuine</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="14" t="inlineStr"/>
-      <c r="J17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
       <c r="K17" s="7" t="inlineStr"/>
       <c r="L17" s="7" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="8" t="inlineStr"/>
+      <c r="N17" s="7" t="inlineStr"/>
+      <c r="O17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
@@ -3275,36 +3368,41 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
+          <t>R14, R25</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
           <t>SC-07, SC-08</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>gate</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>Design logic</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t>Zero rows when governance matches the declared baseline; one row for each injected defect</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr"/>
-      <c r="I18" s="18" t="inlineStr"/>
-      <c r="J18" s="19" t="inlineStr"/>
+      <c r="I18" s="17" t="inlineStr"/>
+      <c r="J18" s="18" t="inlineStr"/>
       <c r="K18" s="19" t="inlineStr"/>
       <c r="L18" s="19" t="inlineStr"/>
       <c r="M18" s="19" t="inlineStr"/>
-      <c r="N18" s="16" t="inlineStr"/>
+      <c r="N18" s="19" t="inlineStr"/>
+      <c r="O18" s="16" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
@@ -3319,40 +3417,45 @@
       </c>
       <c r="C19" s="16" t="inlineStr">
         <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
           <t>SC-06</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="E19" s="16" t="inlineStr">
         <is>
           <t>O10</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>01_governance_survival.sql</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="G19" s="16" t="inlineStr">
         <is>
           <t>Inference, not documented</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="H19" s="16" t="inlineStr">
         <is>
           <t>Real value reads back in the clear once the policy is unbound, proving storage was never masked</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="I19" s="18" t="inlineStr"/>
-      <c r="J19" s="19" t="inlineStr"/>
+      <c r="J19" s="18" t="inlineStr"/>
       <c r="K19" s="19" t="inlineStr"/>
       <c r="L19" s="19" t="inlineStr"/>
       <c r="M19" s="19" t="inlineStr"/>
-      <c r="N19" s="16" t="inlineStr">
+      <c r="N19" s="19" t="inlineStr"/>
+      <c r="O19" s="16" t="inlineStr">
         <is>
           <t>Underpins all of Part B. If storage were masked on write, losing a tag would be harmless and R15 would not exist. Replaces the claim previously resting on an earlier POC capture</t>
         </is>
@@ -3371,40 +3474,45 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
+          <t>R1, R2, R3, R6, R7</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
           <t>SC-02, SC-03, SC-13</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>O11</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>02_atomicity_publication.sql</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>ASSUMPTION: the reader NEVER observes distinct_cycles = 2. All old before COMMIT, all new after</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr"/>
-      <c r="J20" s="9" t="inlineStr"/>
+      <c r="J20" s="21" t="inlineStr"/>
       <c r="K20" s="9" t="inlineStr"/>
       <c r="L20" s="9" t="inlineStr"/>
       <c r="M20" s="9" t="inlineStr"/>
-      <c r="N20" s="10" t="inlineStr"/>
+      <c r="N20" s="9" t="inlineStr"/>
+      <c r="O20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
@@ -3419,36 +3527,41 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
           <t>SC-16</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>O9</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>02_atomicity_publication.sql</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>ASSUMPTION: grants follow the OBJECT, not the name. The ALTER TABLE page is silent on this</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="14" t="inlineStr"/>
-      <c r="J21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="14" t="inlineStr"/>
       <c r="K21" s="7" t="inlineStr"/>
       <c r="L21" s="7" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
@@ -3463,36 +3576,41 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
+          <t>R5, R14</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
           <t>SC-16</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr">
         <is>
           <t>O16</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="F22" s="8" t="inlineStr">
         <is>
           <t>02_atomicity_publication.sql</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>Partly verified</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Documented: privileges on the schemas and their objects swap. UNDOCUMENTED: can the reporting role still query STG.* after the swap?</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="14" t="inlineStr"/>
-      <c r="J22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="14" t="inlineStr"/>
       <c r="K22" s="7" t="inlineStr"/>
       <c r="L22" s="7" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
@@ -3507,36 +3625,41 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
+          <t>R2, R3, R6</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
           <t>SC-02, SC-13</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr">
         <is>
           <t>O16</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="F23" s="8" t="inlineStr">
         <is>
           <t>02_atomicity_publication.sql</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>POC evidence</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="H23" s="8" t="inlineStr">
         <is>
           <t>A query beginning before the swap returns one whole consistent cycle. Extends POC02's held-open join to 4 objects</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="14" t="inlineStr"/>
-      <c r="J23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="14" t="inlineStr"/>
       <c r="K23" s="7" t="inlineStr"/>
       <c r="L23" s="7" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="8" t="inlineStr"/>
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
@@ -3551,36 +3674,41 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
           <t>SC-10</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t>O11</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
         <is>
           <t>02_atomicity_publication.sql</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="H24" s="8" t="inlineStr">
         <is>
           <t>After ROLLBACK the published group is unchanged by the abandoned cycle</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="14" t="inlineStr"/>
-      <c r="J24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr"/>
+      <c r="J24" s="14" t="inlineStr"/>
       <c r="K24" s="7" t="inlineStr"/>
       <c r="L24" s="7" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
-      <c r="N24" s="8" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+      <c r="O24" s="8" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
@@ -3595,36 +3723,41 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
+          <t>R1, R2, R5</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
           <t>SC-01, SC-13</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
         <is>
           <t>O10</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t>02_atomicity_publication.sql</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="H25" s="8" t="inlineStr">
         <is>
           <t>The reader's rowcount is always the old count or the new count. Never 0, never a partial count</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="14" t="inlineStr"/>
-      <c r="J25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="14" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr"/>
       <c r="L25" s="7" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="8" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+      <c r="O25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
@@ -3639,36 +3772,41 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
+          <t>R2, R5</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
           <t>SC-01</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>02_atomicity_publication.sql</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>The reader DOES observe 0 rows. Evidence that a TRUNCATE-then-load pattern cannot satisfy Part A</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="14" t="inlineStr"/>
-      <c r="J26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr"/>
+      <c r="J26" s="14" t="inlineStr"/>
       <c r="K26" s="7" t="inlineStr"/>
       <c r="L26" s="7" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
-      <c r="N26" s="8" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+      <c r="O26" s="8" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
@@ -3683,36 +3821,41 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
+          <t>R3, R20</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>O11</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="F27" s="8" t="inlineStr">
         <is>
           <t>03_views_shape_dependencies.sql</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>Design logic</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>mixed_rows = 0 before and after publication; the view's DDL is byte-identical throughout</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="14" t="inlineStr"/>
-      <c r="J27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="14" t="inlineStr"/>
       <c r="K27" s="7" t="inlineStr"/>
       <c r="L27" s="7" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="8" t="inlineStr"/>
+      <c r="N27" s="7" t="inlineStr"/>
+      <c r="O27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
@@ -3727,36 +3870,41 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="D28" s="8" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>O16</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>03_views_shape_dependencies.sql</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>The view returns the new cycle without being edited. Proves C1 holds for O16</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="14" t="inlineStr"/>
-      <c r="J28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="14" t="inlineStr"/>
       <c r="K28" s="7" t="inlineStr"/>
       <c r="L28" s="7" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="8" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+      <c r="O28" s="8" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
@@ -3771,36 +3919,41 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
           <t>SC-04</t>
         </is>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>O16</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>03_views_shape_dependencies.sql</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>POC evidence</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>After the swap at least one of the two names resolves to the wrong storage. Why views live outside the swapped pair</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="14" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="14" t="inlineStr"/>
       <c r="K29" s="7" t="inlineStr"/>
       <c r="L29" s="7" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="8" t="inlineStr"/>
+      <c r="N29" s="7" t="inlineStr"/>
+      <c r="O29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="20" t="inlineStr">
@@ -3815,36 +3968,41 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
           <t>SC-17</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr">
+      <c r="E30" s="10" t="inlineStr">
         <is>
           <t>O8, O10</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>03_views_shape_dependencies.sql</t>
         </is>
       </c>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G30" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>INSERT OVERWRITE target keeps CLUSTER BY; the CTAS target has no cluster_by</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr"/>
-      <c r="I30" s="21" t="inlineStr"/>
-      <c r="J30" s="9" t="inlineStr"/>
+      <c r="I30" s="9" t="inlineStr"/>
+      <c r="J30" s="21" t="inlineStr"/>
       <c r="K30" s="9" t="inlineStr"/>
       <c r="L30" s="9" t="inlineStr"/>
       <c r="M30" s="9" t="inlineStr"/>
-      <c r="N30" s="10" t="inlineStr"/>
+      <c r="N30" s="9" t="inlineStr"/>
+      <c r="O30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
@@ -3859,36 +4017,41 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
           <t>SC-18</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>O8, O10, O16</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>03_views_shape_dependencies.sql</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>ASSUMPTION: INSERT OVERWRITE advances the stream normally; OR REPLACE leaves it stale. Capture the exact error</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="14" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr"/>
+      <c r="J31" s="14" t="inlineStr"/>
       <c r="K31" s="7" t="inlineStr"/>
       <c r="L31" s="7" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="8" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+      <c r="O31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="20" t="inlineStr">
@@ -3903,36 +4066,41 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
           <t>SC-02</t>
         </is>
       </c>
-      <c r="D32" s="10" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>O11</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>02_atomicity_publication.sql</t>
         </is>
       </c>
-      <c r="F32" s="10" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G32" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>The DDL commits the preceding statement, so ROLLBACK leaves a MIXED state published. Justifies a hard build rule</t>
         </is>
       </c>
-      <c r="H32" s="9" t="inlineStr"/>
-      <c r="I32" s="21" t="inlineStr"/>
-      <c r="J32" s="9" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr"/>
+      <c r="J32" s="21" t="inlineStr"/>
       <c r="K32" s="9" t="inlineStr"/>
       <c r="L32" s="9" t="inlineStr"/>
       <c r="M32" s="9" t="inlineStr"/>
-      <c r="N32" s="10" t="inlineStr"/>
+      <c r="N32" s="9" t="inlineStr"/>
+      <c r="O32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
@@ -3947,36 +4115,41 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
           <t>SC-21</t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>O14</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>03_views_shape_dependencies.sql</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>ASSUMPTION: supported, since v3 documents INSERT and TRUNCATE. Needs an external volume, else record as Blocked</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="14" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="14" t="inlineStr"/>
       <c r="K33" s="7" t="inlineStr"/>
       <c r="L33" s="7" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
-      <c r="N33" s="8" t="inlineStr"/>
+      <c r="N33" s="7" t="inlineStr"/>
+      <c r="O33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
@@ -3991,36 +4164,41 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
+          <t>R8, R9</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
           <t>SC-10</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>gate</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>04_gate_rollback_control.sql</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>Design logic</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>At least one gate check FAILs; the publish is not attempted; the published cycle is unchanged</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="14" t="inlineStr"/>
-      <c r="J34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr"/>
+      <c r="J34" s="14" t="inlineStr"/>
       <c r="K34" s="7" t="inlineStr"/>
       <c r="L34" s="7" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
-      <c r="N34" s="8" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr"/>
+      <c r="O34" s="8" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
@@ -4035,36 +4213,41 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
+          <t>R10, R11</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
           <t>SC-11</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>gate</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="F35" s="8" t="inlineStr">
         <is>
           <t>04_gate_rollback_control.sql</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>Design logic</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="H35" s="8" t="inlineStr">
         <is>
           <t>Authorisation record names who, when, why and which jobs failed. Publication logged as AUTHORISED_PARTIAL</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="14" t="inlineStr"/>
-      <c r="J35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr"/>
+      <c r="J35" s="14" t="inlineStr"/>
       <c r="K35" s="7" t="inlineStr"/>
       <c r="L35" s="7" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
-      <c r="N35" s="8" t="inlineStr"/>
+      <c r="N35" s="7" t="inlineStr"/>
+      <c r="O35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
@@ -4079,36 +4262,41 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
+          <t>R29</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
           <t>SC-12</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>O16</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>04_gate_rollback_control.sql</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="H36" s="8" t="inlineStr">
         <is>
           <t>One further ALTER SCHEMA SWAP WITH returns consumers to the previous version</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="14" t="inlineStr"/>
-      <c r="J36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr"/>
+      <c r="J36" s="14" t="inlineStr"/>
       <c r="K36" s="7" t="inlineStr"/>
       <c r="L36" s="7" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
-      <c r="N36" s="8" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
+      <c r="O36" s="8" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
@@ -4123,36 +4311,41 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
+          <t>R29</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
           <t>SC-12</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>O11</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>04_gate_rollback_control.sql</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
         <is>
           <t>One more transaction restores the prior version. The window closes when the next cycle overwrites staging</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="14" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr"/>
+      <c r="J37" s="14" t="inlineStr"/>
       <c r="K37" s="7" t="inlineStr"/>
       <c r="L37" s="7" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr"/>
+      <c r="N37" s="7" t="inlineStr"/>
+      <c r="O37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
@@ -4167,36 +4360,41 @@
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
+          <t>R11, R19</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
           <t>SC-07</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>gate</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>04_gate_rollback_control.sql</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>Design logic</t>
         </is>
       </c>
-      <c r="G38" s="16" t="inlineStr">
+      <c r="H38" s="16" t="inlineStr">
         <is>
           <t>One row per group per cycle, and a staleness query Ops can alert on</t>
         </is>
       </c>
-      <c r="H38" s="17" t="inlineStr"/>
-      <c r="I38" s="18" t="inlineStr"/>
-      <c r="J38" s="19" t="inlineStr"/>
+      <c r="I38" s="17" t="inlineStr"/>
+      <c r="J38" s="18" t="inlineStr"/>
       <c r="K38" s="19" t="inlineStr"/>
       <c r="L38" s="19" t="inlineStr"/>
       <c r="M38" s="19" t="inlineStr"/>
-      <c r="N38" s="16" t="inlineStr"/>
+      <c r="N38" s="19" t="inlineStr"/>
+      <c r="O38" s="16" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
@@ -4211,40 +4409,45 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
+          <t>R25</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
           <t>SC-08</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>O10, O16</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>04_gate_rollback_control.sql</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>Not documented</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>ASSUMPTION: O10 leaves it removed; O16 REINSTATES it unless the gate reconciled staging first</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="I39" s="14" t="inlineStr"/>
-      <c r="J39" s="7" t="inlineStr"/>
+      <c r="J39" s="14" t="inlineStr"/>
       <c r="K39" s="7" t="inlineStr"/>
       <c r="L39" s="7" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
-      <c r="N39" s="8" t="inlineStr"/>
+      <c r="N39" s="7" t="inlineStr"/>
+      <c r="O39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
@@ -4259,36 +4462,41 @@
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
           <t>SC-19</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>05_sizing_performance.sql</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>Design logic</t>
         </is>
       </c>
-      <c r="G40" s="16" t="inlineStr">
+      <c r="H40" s="16" t="inlineStr">
         <is>
           <t>A list materially shorter than the full view estate. That gap is the saving from gating only what is consumed</t>
         </is>
       </c>
-      <c r="H40" s="17" t="inlineStr"/>
-      <c r="I40" s="18" t="inlineStr"/>
-      <c r="J40" s="19" t="inlineStr"/>
+      <c r="I40" s="17" t="inlineStr"/>
+      <c r="J40" s="18" t="inlineStr"/>
       <c r="K40" s="19" t="inlineStr"/>
       <c r="L40" s="19" t="inlineStr"/>
       <c r="M40" s="19" t="inlineStr"/>
-      <c r="N40" s="16" t="inlineStr"/>
+      <c r="N40" s="19" t="inlineStr"/>
+      <c r="O40" s="16" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
@@ -4303,40 +4511,45 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
+          <t>R4, R22</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
           <t>SC-19</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>O11, O16</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>05_sizing_performance.sql</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>Design logic</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>tables_to_gate per schema = the effort number. Any schemas_spanned &gt; 1 means O16 is not viable for that group</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>CRITICAL</t>
         </is>
       </c>
-      <c r="I41" s="14" t="inlineStr"/>
-      <c r="J41" s="7" t="inlineStr"/>
+      <c r="J41" s="14" t="inlineStr"/>
       <c r="K41" s="7" t="inlineStr"/>
       <c r="L41" s="7" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="8" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
+      <c r="O41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
@@ -4351,36 +4564,41 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
           <t>SC-20</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>O8, O10</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>05_sizing_performance.sql</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>No benchmark</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>Expect broadly comparable, SELECT-dominated. Record median seconds, GB written, and whether clustering survived</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="14" t="inlineStr"/>
-      <c r="J42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr"/>
+      <c r="J42" s="14" t="inlineStr"/>
       <c r="K42" s="7" t="inlineStr"/>
       <c r="L42" s="7" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
-      <c r="N42" s="8" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+      <c r="O42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
@@ -4395,36 +4613,41 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
           <t>SC-20</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>O8, O10</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="F43" s="8" t="inlineStr">
         <is>
           <t>05_sizing_performance.sql</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>No benchmark</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>As TC-050 at 60 columns, to see whether width changes the relationship</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="14" t="inlineStr"/>
-      <c r="J43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr"/>
+      <c r="J43" s="14" t="inlineStr"/>
       <c r="K43" s="7" t="inlineStr"/>
       <c r="L43" s="7" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
-      <c r="N43" s="8" t="inlineStr"/>
+      <c r="N43" s="7" t="inlineStr"/>
+      <c r="O43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
@@ -4439,36 +4662,41 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
           <t>SC-20</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>O11</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>05_sizing_performance.sql</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>No benchmark</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>The cost of the second write. Must stay well inside the documented 4-hour non-blocking transaction limit</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="14" t="inlineStr"/>
-      <c r="J44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr"/>
+      <c r="J44" s="14" t="inlineStr"/>
       <c r="K44" s="7" t="inlineStr"/>
       <c r="L44" s="7" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
-      <c r="N44" s="8" t="inlineStr"/>
+      <c r="N44" s="7" t="inlineStr"/>
+      <c r="O44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
@@ -4483,36 +4711,41 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
           <t>SC-20</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="E45" s="8" t="inlineStr">
         <is>
           <t>O16</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="F45" s="8" t="inlineStr">
         <is>
           <t>05_sizing_performance.sql</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>No benchmark</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="H45" s="8" t="inlineStr">
         <is>
           <t>Expect effectively constant and sub-second regardless of volume. TC-052 vs TC-053 is the trade-off made concrete</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr"/>
       <c r="J45" s="7" t="inlineStr"/>
       <c r="K45" s="7" t="inlineStr"/>
       <c r="L45" s="7" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
-      <c r="N45" s="8" t="inlineStr"/>
+      <c r="N45" s="7" t="inlineStr"/>
+      <c r="O45" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6113,4 +6346,739 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="95" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="B1" s="25" t="inlineStr">
+        <is>
+          <t>Part</t>
+        </is>
+      </c>
+      <c r="C1" s="25" t="inlineStr">
+        <is>
+          <t>Covered by</t>
+        </is>
+      </c>
+      <c r="D1" s="25" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" s="25" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TC-020, TC-025</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TC-020, TC-023, TC-025, TC-026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TC-020, TC-023, TC-027, TC-032</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E4" s="26" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TC-041</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>TC-041 reveals overlap but does not prove non-interference. Needs the connected-components check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TC-022, TC-025, TC-026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TC-020, TC-023</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E7" s="26" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TC-020</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TC-034</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TC-024, TC-034</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TC-035</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TC-035, TC-038</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>NO TEST</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
+        <is>
+          <t>Reduces to "publication is re-runnable within a cycle" under assumption A5. Worth one test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>NO TEST</t>
+        </is>
+      </c>
+      <c r="E14" s="28" t="inlineStr">
+        <is>
+          <t>Unreachable under A5 (batches strictly serialised). No test needed while A5 holds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TC-001, TC-002, TC-003, TC-004, TC-005, TC-007, TC-008, TC-009, TC-010, TC-015, TC-021, TC-022</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TC-014, TC-016</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TC-010</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TC-011, TC-012</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TC-003, TC-006</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TC-038</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TC-005b, TC-027, TC-028, TC-029</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E21" s="26" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TC-013, TC-031, TC-033</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TC-040, TC-041</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E23" s="26" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TC-030, TC-050, TC-051, TC-052, TC-053</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E24" s="26" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>R24</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>Shared</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>NO TEST</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
+        <is>
+          <t>Storage overhead not measured. TC-052/053 time the publish, they do not size the retained copy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TC-015, TC-039</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E26" s="26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>R26</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>NO TEST</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="inlineStr">
+        <is>
+          <t>No row access policy exists in the POC fixture. Add one, or record that none exists in Zone 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TC-014</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>R28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TC-005</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E29" s="26" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TC-036, TC-037</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Covered</t>
+        </is>
+      </c>
+      <c r="E30" s="26" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>